--- a/output/lgbm_clf/02_feature_selection/特征筛选报告.xlsx
+++ b/output/lgbm_clf/02_feature_selection/特征筛选报告.xlsx
@@ -500,7 +500,7 @@
         <v>0.08500000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5786</v>
+        <v>2.1123</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1208,31 +1208,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>f1</t>
+          <t>f2</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.6651</v>
+        <v>2.1123</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>f3</t>
+          <t>f1</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.6425</v>
+        <v>1.6651</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>f2</t>
+          <t>f3</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.5786</v>
+        <v>1.6425</v>
       </c>
     </row>
     <row r="6">
